--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/10_ai_automation_use_cases.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/10_ai_automation_use_cases.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R7f87782a5ce345e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rfcca040ca4924825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rae1cb66e47e34f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R0f3cb592935f4ce7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R76a6a5c791774f19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rb12cbe57accf4b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R04c9c47ae7f94e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R1dd8980296bf4dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R2d97daad20c54f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rc5b34e934cc44e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R35e9fff705aa496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R76d0418eebe04a45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -626,7 +626,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7fc67faf97843fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26ddb967a0464d3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -797,7 +797,7 @@
         <x:v>Chief Strategy Officer</x:v>
       </x:c>
       <x:c r="N6" s="78" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Executive Office context and decision assistant (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -844,7 +844,7 @@
         <x:v>CMO</x:v>
       </x:c>
       <x:c r="N7" s="79" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm Provider Operations context and decision assistant (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -891,7 +891,7 @@
         <x:v>Health Plan COO</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Attach client evidence for Claims Operations context and decision assistant (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>Medium</x:v>
@@ -938,7 +938,7 @@
         <x:v>VP Benefits Operations</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile Eligibility and Benefits context and decision assistant (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O9" t="str">
         <x:v>Medium</x:v>
@@ -985,7 +985,7 @@
         <x:v>VP Utilization Management</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior authorization / utilization management AI-enabled workflow (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O10" t="str">
         <x:v>Medium</x:v>
@@ -1032,7 +1032,7 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Contact Center and Member Service context and decision assistant (record 6) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O11" t="str">
         <x:v>Medium</x:v>
@@ -1079,7 +1079,7 @@
         <x:v>Revenue Cycle Leader</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm Revenue Cycle Operations context and decision assistant (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O12" t="str">
         <x:v>Medium</x:v>
@@ -1126,7 +1126,7 @@
         <x:v>CFO</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Finance Analytics context and decision assistant (record 8) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O13" t="str">
         <x:v>Medium</x:v>
@@ -1173,7 +1173,7 @@
         <x:v>CHRO</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile Workforce Analytics context and decision assistant (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O14" t="str">
         <x:v>Medium</x:v>
@@ -1220,7 +1220,7 @@
         <x:v>VP Quality</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics context and decision assistant (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O15" t="str">
         <x:v>Medium</x:v>
@@ -1267,7 +1267,7 @@
         <x:v>VP Claims Analytics</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Claims and Payment Analytics context and decision assistant (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O16" t="str">
         <x:v>Medium</x:v>
@@ -1314,7 +1314,7 @@
         <x:v>VP Provider Performance</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm Provider Performance Analytics context and decision assistant (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O17" t="str">
         <x:v>Medium</x:v>
@@ -1361,7 +1361,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Attach client evidence for Enterprise Data Platform context and decision assistant (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O18" t="str">
         <x:v>Medium</x:v>
@@ -1408,7 +1408,7 @@
         <x:v>Chief Data Officer</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile Data Governance and Data Quality context and decision assistant (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O19" t="str">
         <x:v>Medium</x:v>
@@ -1455,7 +1455,7 @@
         <x:v>VP Contact Center</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Agent Assist for member service AI-enabled workflow (record 15) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>Medium</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse context and decision assistant (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O21" t="str">
         <x:v>Medium</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>CIO / CFO</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline context and decision assistant (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>Medium</x:v>
@@ -1596,7 +1596,7 @@
         <x:v>Chief Procurement Officer</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization context and decision assistant (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>Medium</x:v>
@@ -1643,7 +1643,7 @@
         <x:v>CTO</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile Infrastructure and CMDB context and decision assistant (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>Medium</x:v>
@@ -1690,7 +1690,7 @@
         <x:v>VP IT Operations</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations context and decision assistant (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O25" t="str">
         <x:v>Medium</x:v>
@@ -1714,7 +1714,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3c658d6e9e44f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd93bfbc0bd834bbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1789,7 +1789,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3143e5bd4d4c463a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea2b1d2751684961"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1973,7 +1973,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra856b13bcd19444d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38bf3e8a1d794e83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2043,7 +2043,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb164a71de2534fac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec5426d2076b4cea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2153,7 +2153,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d0cf9bb4ae64ce0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra27585baa39b4e1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>